--- a/Outputs/Scenarios/PtX_demand_NL_Hydrogen.xlsx
+++ b/Outputs/Scenarios/PtX_demand_NL_Hydrogen.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.001347394788327499</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0289379125055472</v>
+        <v>0.01762961379460802</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.009645970835182403</v>
+        <v>0.02142016826691279</v>
       </c>
     </row>
     <row r="18">
@@ -1481,7 +1481,7 @@
         <v>1.941367814293906e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.009645970835182403</v>
+        <v>0.009180072114391199</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.001994653943655183</v>
       </c>
       <c r="K30" t="n">
-        <v>0.1548883243404942</v>
+        <v>0.09436137934598621</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0516294414468314</v>
+        <v>0.1146500795217196</v>
       </c>
     </row>
     <row r="32">
@@ -1999,7 +1999,7 @@
         <v>0.0001049817865081676</v>
       </c>
       <c r="K42" t="n">
-        <v>0.0516294414468314</v>
+        <v>0.04913574836645125</v>
       </c>
     </row>
     <row r="43">
